--- a/語文補給站_教材部署清單總覽.xlsx
+++ b/語文補給站_教材部署清單總覽.xlsx
@@ -1,23 +1,25 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
-  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
-  <AppVersion>3.1</AppVersion>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教材部署清單" sheetId="1" state="visible" r:id="rId1"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'教材部署清單'!$A$1:$G$36</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
-  <dc:creator xmlns:dc="http://purl.org/dc/elements/1.1/">openpyxl</dc:creator>
-  <dcterms:created xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-08-19T15:55:15Z</dcterms:created>
-  <dcterms:modified xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-08-19T15:55:15Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,30 +31,27 @@
       <name val="微軟正黑體"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微軟正黑體"/>
+      <color rgb="001E293B"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="微軟正黑體"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
+      <color rgb="000F172A"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="微軟正黑體"/>
       <color rgb="002563EB"/>
       <sz val="10"/>
       <u val="single"/>
     </font>
-    <font>
-      <name val="微軟正黑體"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -67,20 +66,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002563EB"/>
-        <bgColor rgb="002563EB"/>
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
-        <bgColor rgb="00F8FAFC"/>
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F3FF"/>
+        <bgColor rgb="00F5F3FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,37 +115,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -218,7 +220,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -501,700 +503,1324 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="語文補給站部署清單" sheetId="1" state="visible" r:id="rId1"/>
-  </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="68" customWidth="1" min="6" max="6"/>
-    <col width="58" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+    <col width="55" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>學思軒?語文補給站｜國語文 AI 數位互動教材部署總覽表</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
           <t>序號</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>單元分類</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>單元名稱</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>對應課文/範疇</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>檔案相對路徑</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>GitHub_Pages線上網址</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>核心功能特色</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>單元分類</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>單元名稱</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>對應課文/範疇</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>檔案相對路徑</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>GitHub Pages 線上完整網址</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>核心功能特色</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>首頁總覽</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>學思軒?語文補給站 數位互動教材總入口</t>
+          <t>總入口網頁</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>學思軒・語文補給站 數位互動教材總入口</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>全站總導覽・全資源索引</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>index.html</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/index.html</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>整合11大旗艦殿堂與23款練習神器、關鍵字即時搜尋、跨載具自適應</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>旗艦學習殿堂</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>「賓語提前」倒裝句法旗艦殿堂</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>全站總導覽?全資源索引</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>index.html</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/index.html</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>整合4大旗艦殿堂與12款練習神器、關鍵字即時搜尋、跨載具自適應</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
+          <t>翰林國文 B3L04《愛蓮說》</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>inversion.html</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/inversion.html</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>刺蝟口訣、五步還原法、16組典範圖鑑(全真人語音)、魔法工坊、會考挑戰賽</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>旗艦學習殿堂</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>「賓語提前」倒裝句法旗艦殿堂</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>移覺（通感）修辭互動學習殿堂</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L01《田園之秋選》</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>yijay.html</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/yijay.html</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>五感羅盤互動、30句典範圖鑑(真人語音)、造句魔法工坊、會考實戰闖關</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>旗艦學習殿堂</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>時序之美：傳統節日與二十四節氣殿堂</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>國學常識・跨科天文曆法</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>holiday.html</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday.html</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>曆法大解密、10大傳統節日深度探索、20題詩詞密碼獵手、會考神射手測驗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>旗艦學習殿堂</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>詞類與詞性・AI 互動學習殿堂</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 語文常識（一）</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>pos.html</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos.html</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>字詞句層級、實詞虛詞全圖鑑、複詞音韻探索、100題流行歌詞庫(真人語音)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>旗艦學習殿堂</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>花花語文世界：植物象徵・名花物語旗艦殿堂</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>翰林國文 B3L04《愛蓮說》</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>inversion.html</t>
-        </is>
-      </c>
-      <c r="F4" s="10" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/inversion.html</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>刺蝟口訣、五步還原法、16組典範圖鑑(全真人語音)、魔法工坊、會考神仙挑戰賽</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>flower.html</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower.html</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>9大植物象徵圖鑑(真人語音)、5大名花代言人、幽夢影知己圖譜、人比花嬌是非辨析、會考挑戰賽、造句工坊</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>旗艦學習殿堂</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>移覺（通感）修辭互動學習殿堂</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>翰林國文 B3L01《田園之秋選》</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>yijay.html</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/yijay.html</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>五感羅盤互動、30句典範圖鑑(真人語音)、造句魔法工坊、會考實戰闖關</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>中外俗諺大觀園・旗艦學習殿堂</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L05《生命中的碎珠》</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>proverb.html</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb.html</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>36組中外俗諺全圖鑑(真人語音)、抽喻體解題三部曲、文化星盤、尋伴工坊、會考神射手測驗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>旗艦學習殿堂</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>時序之美：傳統節日與二十四節氣殿堂</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>國學常識?跨科天文曆法</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>holiday.html</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday.html</t>
-        </is>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>曆法大解密、10大傳統節日深度探索、20題詩詞密碼獵手、會考神射手測驗</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>萬籟俱寂・聲歷其境——狀聲詞旗艦學習殿堂</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L06《鳥》</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>onomatopoeia.html</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/onomatopoeia.html</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>45+組典範聲景圖鑑(全真人語音)、橘老師開唱解題避坑指南、古典聲景魔法工坊、會考神仙挑戰賽</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>旗艦學習殿堂</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>詞類與詞性?AI 互動學習殿堂</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>翰林國文 語文常識（一）</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>pos.html</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos.html</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>字詞句層級、實詞虛詞全圖鑑、複詞音韻探索、100題流行歌詞庫(真人語音)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>五彩斑斕——顏色字判斷旗艦學習殿堂</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L06《鳥》</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>color.html</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/color.html</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>103組顏色字全圖鑑(全真人語音)、實指非指雙色對比、五大色系文化羅盤、會考神仙挑戰賽、專屬練習神器內嵌</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>旗艦學習殿堂</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>詩中的鳥類・古典禽鳥意象旗艦殿堂</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L06《鳥》</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>bird.html</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/bird.html</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>52種古典詩詞禽鳥圖鑑(全真人語音)、八大文化象徵星盤、15字極簡速記口訣卡、神仙挑戰賽</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>旗艦學習殿堂</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>疊字詞・聲情神采與疊韻之美旗艦殿堂</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L02《古詩選》</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>reduplication.html</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication.html</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>54組經典疊字詞全圖鑑(全真人語音)、多義疊字深度對決、五大情意星盤、橘老師開唱解題避坑指南、詩境魔法工坊、會考神仙挑戰賽、專屬練習神器內嵌</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>旗艦學習殿堂</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>古典詩境・詩詞表現手法與常見意象殿堂</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L02《古詩選》</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>poetry.html</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry.html</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>六大表現手法解構、四大維度51款古典意象(全真人語音)、詩境造景工坊、會考挑戰賽、雙款練習神器</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>專屬練習神器</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>詩詞表現手法練習神器</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L02《古詩選》</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>poetry/poetry-technique-practice.html</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry/poetry-technique-practice.html</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>41句古典詩詞名句、六大表現手法3D雙面翻卡特訓、即時測驗解析、個人錯題本</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>詩詞常見意象練習神器(51款意象版)</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L02《古詩選》</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>poetry/poetry-imagery-practice.html</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry/poetry-imagery-practice.html</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>51款經典詩詞意象與象徵意涵、雙向翻卡記憶、快速快問快答、錯題精準強化</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>疊字詞練習神器</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L02《古詩選》</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>reduplication/reduplication-words-practice.html</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication/reduplication-words-practice.html</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>101組課內外經典疊字詞、3D雙面翻卡特訓、即時測驗解析、全卷大卷瀏覽、LocalStorage錯題本</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>疊字成語練習神器</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L02《古詩選》</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>reduplication/reduplication-idioms-practice.html</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication/reduplication-idioms-practice.html</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>95組AABB會考高頻疊字成語、雙面翻卡、釋義測驗、情境例句、錯題本特訓</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>詩中的鳥類練習神器</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L06《鳥》</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>bird/bird-practice.html</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/bird/bird-practice.html</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>52種古典詩詞禽鳥意象、3D雙面翻卡特訓、快問快答、全卷瀏覽、個人錯題本</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>節慶（詩詞句）練習神器</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>國學常識・節令文化</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>holiday/festival-poems.html</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/festival-poems.html</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>傳統節日經典詩詞配對、會考高頻詩句辨析、拖曳互動</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>二十四節氣練習神器</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>自然時序・節氣文化</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>holiday/24-solar-terms.html</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/24-solar-terms.html</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>二十四節氣四季排序、季節物候特徵辨析</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>季節（關鍵字詞）練習神器</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>季節詞彙辨析</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>holiday/season-keywords.html</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-keywords.html</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>花卉氣候動植物關鍵線索抓取、快速解題特訓</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>季節（相關詞句）練習神器</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>名句鑑賞・時序判讀</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>holiday/season-verses.html</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-verses.html</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>歷代名篇佳句鑑賞、四時景物描寫語感養成</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>移覺（通感）修辭練習神器</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>核心修辭特訓</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>yijay/synesthesia-practice.html</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/yijay/synesthesia-practice.html</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>30組感官轉換試題、感官互移判定、手感記憶特訓</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>「賓語提前」倒裝句練習神器</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>翰林國文 B3L04《愛蓮說》</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>inversion/inversion-practice.html</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>https://oaoadna-1313.github.io/2026_languagecorner/inversion/inversion-practice.html</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>3D雙面翻卡特訓、高誘答力闖關測驗、公式秘笈隨身查</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>專屬練習神器</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>移覺（通感）修辭練習神器</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>核心修辭特訓</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>yijay/synesthesia-practice.html</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/yijay/synesthesia-practice.html</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>30組感官轉換試題、感官互移判定、手感記憶特訓</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>花花語文世界專屬練習神器</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L04《愛蓮說》</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>flower/flower-practice.html</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower/flower-practice.html</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>26組3D雙面翻卡特訓、名花知己連連看配對、人比花嬌是非快打、錯題收藏本</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>專屬練習神器</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>節慶（詩詞句）練習神器</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>國學常識?節令文化</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>holiday/festival-poems.html</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/festival-poems.html</t>
-        </is>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
-        <is>
-          <t>傳統節日經典詩詞配對、會考高頻詩句辨析</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>詩詞常見意象練習神器(36大意象版)</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>國學常識・詩詞意象</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>flower/poetry-imagery.html</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower/poetry-imagery.html</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>36大常見意象、翻卡記憶、意象測驗、詩詞測驗、智慧錯題本</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>專屬練習神器</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>二十四節氣練習神器</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>自然時序?節氣文化</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>holiday/24-solar-terms.html</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/24-solar-terms.html</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>二十四節氣四季排序、季節物候特徵辨析</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>中外俗諺對照練習神器</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L05《生命中的碎珠》</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>proverb/proverb-practice.html</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb/proverb-practice.html</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>36組3D雙面翻卡特訓、隨機10題闖關測驗、中外俗諺對照全覽表</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="8" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>專屬練習神器</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>季節（關鍵字詞）練習神器</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>季節詞彙辨析</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>holiday/season-keywords.html</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-keywords.html</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t>花卉氣候動植物關鍵線索抓取、快速解題特訓</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>古文格言練習神器</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>國學常識・經典名言</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>proverb/proverb-aphorism.html</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb/proverb-aphorism.html</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>歷代經典古文格言、3D雙面翻卡、白話翻譯、核心道理闡釋、錯題特訓</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="8" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>專屬練習神器</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>季節（相關詞句）練習神器</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>名句鑑賞?時序判讀</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>holiday/season-verses.html</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-verses.html</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>歷代名篇佳句鑑賞、四時景物描寫語感養成</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>狀聲詞練習神器</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L06《鳥》</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>onomatopoeia/onomatopoeia-practice.html</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/onomatopoeia/onomatopoeia-practice.html</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>62組3D雙面翻卡特訓、四選一釋義測驗、語句填空挑戰、LocalStorage錯題本</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>顏色字判斷練習神器</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L06《鳥》</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>color/color-practice.html</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/color/color-practice.html</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>98組3D雙面翻卡特訓、快問快答測驗、大卷練習、LocalStorage錯題本</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>跨庫整合神器</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C31" s="3" t="inlineStr">
         <is>
           <t>同義反義偏義複詞練習神器</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>複詞構造?規則判斷</t>
-        </is>
-      </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>複詞構造・規則判斷</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>(practicetools)</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-compound-words.html</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>偏義複詞重點突破、同義反義構詞判斷</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>跨庫整合神器</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>量詞運用練習神器</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>計量單位?語法搭配</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>計量單位・語法搭配</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>(practicetools)</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-classifiers.html</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>名量詞動量詞精準搭配、生活與古漢語量詞</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>跨庫整合神器</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>連接詞運用練習神器</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>複句關係?邏輯關聯</t>
-        </is>
-      </c>
-      <c r="E16" s="9" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>複句關係・邏輯關聯</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>(practicetools)</t>
         </is>
       </c>
-      <c r="F16" s="10" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-conjunctions.html</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>因果轉折遞進條件關聯詞選用、邏輯銜接強化</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>跨庫整合神器</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>詞性判斷練習神器</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>實詞虛詞?精準定位</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>實詞虛詞・精準定位</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>(practicetools)</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-part-of-speech.html</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>十大詞性精準定位、實詞虛詞文法判定</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>跨庫整合神器</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C35" s="3" t="inlineStr">
         <is>
           <t>詞性活用判斷練習神器</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>轉品活用?文言解析</t>
-        </is>
-      </c>
-      <c r="E18" s="9" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>轉品活用・文言解析</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>(practicetools)</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-pos-inflection.html</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>名詞作動詞形容詞作動詞、文言位置決定詞性</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="3" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>跨庫整合神器</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C36" s="3" t="inlineStr">
         <is>
           <t>詞性結構判斷練習神器</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>四字成語?結構拆解</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>四字成語・結構拆解</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>(practicetools)</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-pos-structure.html</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>名動名動副形副形等成語結構快速分析</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
+  <autoFilter ref="A1:G36"/>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/語文補給站_教材部署清單總覽.xlsx
+++ b/語文補給站_教材部署清單總覽.xlsx
@@ -51,7 +51,7 @@
       <u val="single"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -82,12 +82,6 @@
         <bgColor rgb="00ECFDF5"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F3FF"/>
-        <bgColor rgb="00F5F3FF"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -115,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -139,9 +133,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -589,7 +580,7 @@
       </c>
       <c r="G2" s="6" t="inlineStr">
         <is>
-          <t>整合11大旗艦殿堂與23款練習神器、關鍵字即時搜尋、跨載具自適應</t>
+          <t>整合11大旗艦殿堂與23款專屬練習神器、關鍵字即時搜尋、跨載具自適應</t>
         </is>
       </c>
     </row>
@@ -729,7 +720,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>字詞句層級、實詞虛詞全圖鑑、複詞音韻探索、100題流行歌詞庫(真人語音)</t>
+          <t>字詞句層級、實詞虛詞全圖鑑、複詞音韻探索、100題流行歌詞庫(真人語音)、六大專屬練習神器內嵌</t>
         </is>
       </c>
     </row>
@@ -989,27 +980,27 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>詩詞表現手法練習神器</t>
+          <t>同義反義偏義複詞練習神器</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 語文常識（一）</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>poetry/poetry-technique-practice.html</t>
+          <t>pos/compound-words-practice.html</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry/poetry-technique-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/compound-words-practice.html</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>41句古典詩詞名句、六大表現手法3D雙面翻卡特訓、即時測驗解析、個人錯題本</t>
+          <t>偏義複詞重點突破、同義反義構詞判斷、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1024,27 +1015,27 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>詩詞常見意象練習神器(51款意象版)</t>
+          <t>量詞運用練習神器</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 語文常識（一）</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>poetry/poetry-imagery-practice.html</t>
+          <t>pos/classifiers-practice.html</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry/poetry-imagery-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/classifiers-practice.html</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>51款經典詩詞意象與象徵意涵、雙向翻卡記憶、快速快問快答、錯題精準強化</t>
+          <t>名量詞動量詞精準搭配、生活與古漢語量詞、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1059,27 +1050,27 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>疊字詞練習神器</t>
+          <t>連接詞運用練習神器</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 語文常識（一）</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>reduplication/reduplication-words-practice.html</t>
+          <t>pos/conjunctions-practice.html</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication/reduplication-words-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/conjunctions-practice.html</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>101組課內外經典疊字詞、3D雙面翻卡特訓、即時測驗解析、全卷大卷瀏覽、LocalStorage錯題本</t>
+          <t>因果轉折遞進條件關聯詞選用、邏輯銜接強化、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1094,27 +1085,27 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>疊字成語練習神器</t>
+          <t>詞性判斷練習神器</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 語文常識（一）</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>reduplication/reduplication-idioms-practice.html</t>
+          <t>pos/part-of-speech-practice.html</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication/reduplication-idioms-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/part-of-speech-practice.html</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>95組AABB會考高頻疊字成語、雙面翻卡、釋義測驗、情境例句、錯題本特訓</t>
+          <t>十大詞性精準定位、實詞虛詞文法判定、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1129,27 +1120,27 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>詩中的鳥類練習神器</t>
+          <t>詞性活用判斷練習神器</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>翰林國文 B3L06《鳥》</t>
+          <t>翰林國文 語文常識（一）</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>bird/bird-practice.html</t>
+          <t>pos/pos-inflection-practice.html</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/bird/bird-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/pos-inflection-practice.html</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>52種古典詩詞禽鳥意象、3D雙面翻卡特訓、快問快答、全卷瀏覽、個人錯題本</t>
+          <t>名詞作動詞形容詞作動詞、轉品活用文言位置解析、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1164,27 +1155,27 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>節慶（詩詞句）練習神器</t>
+          <t>詞性結構判斷練習神器</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>國學常識・節令文化</t>
+          <t>翰林國文 語文常識（一）</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>holiday/festival-poems.html</t>
+          <t>pos/pos-structure-practice.html</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/festival-poems.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/pos-structure-practice.html</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>傳統節日經典詩詞配對、會考高頻詩句辨析、拖曳互動</t>
+          <t>四字成語結構拆解（名動名動、副形副形等）、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1199,27 +1190,27 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>二十四節氣練習神器</t>
+          <t>詩詞表現手法練習神器</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>自然時序・節氣文化</t>
+          <t>翰林國文 B3L02《古詩選》</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>holiday/24-solar-terms.html</t>
+          <t>poetry/poetry-technique-practice.html</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/24-solar-terms.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry/poetry-technique-practice.html</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>二十四節氣四季排序、季節物候特徵辨析</t>
+          <t>41句古典詩詞名句、六大表現手法3D雙面翻卡特訓、即時測驗解析、個人錯題本</t>
         </is>
       </c>
     </row>
@@ -1234,27 +1225,27 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>季節（關鍵字詞）練習神器</t>
+          <t>詩詞常見意象練習神器(51款意象版)</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>季節詞彙辨析</t>
+          <t>翰林國文 B3L02《古詩選》</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>holiday/season-keywords.html</t>
+          <t>poetry/poetry-imagery-practice.html</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-keywords.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry/poetry-imagery-practice.html</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>花卉氣候動植物關鍵線索抓取、快速解題特訓</t>
+          <t>51款經典詩詞意象與象徵意涵、雙向翻卡記憶、快速快問快答、錯題精準強化</t>
         </is>
       </c>
     </row>
@@ -1269,27 +1260,27 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>季節（相關詞句）練習神器</t>
+          <t>疊字詞練習神器</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>名句鑑賞・時序判讀</t>
+          <t>翰林國文 B3L02《古詩選》</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>holiday/season-verses.html</t>
+          <t>reduplication/reduplication-words-practice.html</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-verses.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication/reduplication-words-practice.html</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>歷代名篇佳句鑑賞、四時景物描寫語感養成</t>
+          <t>101組課內外經典疊字詞、3D雙面翻卡特訓、即時測驗解析、全卷大卷瀏覽、LocalStorage錯題本</t>
         </is>
       </c>
     </row>
@@ -1304,27 +1295,27 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>移覺（通感）修辭練習神器</t>
+          <t>疊字成語練習神器</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>核心修辭特訓</t>
+          <t>翰林國文 B3L02《古詩選》</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>yijay/synesthesia-practice.html</t>
+          <t>reduplication/reduplication-idioms-practice.html</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/yijay/synesthesia-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication/reduplication-idioms-practice.html</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>30組感官轉換試題、感官互移判定、手感記憶特訓</t>
+          <t>95組AABB會考高頻疊字成語、雙面翻卡、釋義測驗、情境例句、錯題本特訓</t>
         </is>
       </c>
     </row>
@@ -1339,27 +1330,27 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>「賓語提前」倒裝句練習神器</t>
+          <t>詩中的鳥類練習神器</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>翰林國文 B3L04《愛蓮說》</t>
+          <t>翰林國文 B3L06《鳥》</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>inversion/inversion-practice.html</t>
+          <t>bird/bird-practice.html</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/inversion/inversion-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/bird/bird-practice.html</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>3D雙面翻卡特訓、高誘答力闖關測驗、公式秘笈隨身查</t>
+          <t>52種古典詩詞禽鳥意象、3D雙面翻卡特訓、快問快答、全卷瀏覽、個人錯題本</t>
         </is>
       </c>
     </row>
@@ -1374,27 +1365,27 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>花花語文世界專屬練習神器</t>
+          <t>節慶（詩詞句）練習神器</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>翰林國文 B3L04《愛蓮說》</t>
+          <t>國學常識・節令文化</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>flower/flower-practice.html</t>
+          <t>holiday/festival-poems.html</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower/flower-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/festival-poems.html</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>26組3D雙面翻卡特訓、名花知己連連看配對、人比花嬌是非快打、錯題收藏本</t>
+          <t>傳統節日經典詩詞配對、會考高頻詩句辨析、拖曳互動</t>
         </is>
       </c>
     </row>
@@ -1409,27 +1400,27 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>詩詞常見意象練習神器(36大意象版)</t>
+          <t>二十四節氣練習神器</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>國學常識・詩詞意象</t>
+          <t>自然時序・節氣文化</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>flower/poetry-imagery.html</t>
+          <t>holiday/24-solar-terms.html</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower/poetry-imagery.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/24-solar-terms.html</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>36大常見意象、翻卡記憶、意象測驗、詩詞測驗、智慧錯題本</t>
+          <t>二十四節氣四季排序、季節物候特徵辨析</t>
         </is>
       </c>
     </row>
@@ -1444,27 +1435,27 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>中外俗諺對照練習神器</t>
+          <t>季節（關鍵字詞）練習神器</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>翰林國文 B3L05《生命中的碎珠》</t>
+          <t>季節詞彙辨析</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>proverb/proverb-practice.html</t>
+          <t>holiday/season-keywords.html</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb/proverb-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-keywords.html</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>36組3D雙面翻卡特訓、隨機10題闖關測驗、中外俗諺對照全覽表</t>
+          <t>花卉氣候動植物關鍵線索抓取、快速解題特訓</t>
         </is>
       </c>
     </row>
@@ -1479,27 +1470,27 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>古文格言練習神器</t>
+          <t>季節（相關詞句）練習神器</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>國學常識・經典名言</t>
+          <t>名句鑑賞・時序判讀</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>proverb/proverb-aphorism.html</t>
+          <t>holiday/season-verses.html</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb/proverb-aphorism.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-verses.html</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>歷代經典古文格言、3D雙面翻卡、白話翻譯、核心道理闡釋、錯題特訓</t>
+          <t>歷代名篇佳句鑑賞、四時景物描寫語感養成</t>
         </is>
       </c>
     </row>
@@ -1514,27 +1505,27 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>狀聲詞練習神器</t>
+          <t>移覺（通感）修辭練習神器</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>翰林國文 B3L06《鳥》</t>
+          <t>核心修辭特訓</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>onomatopoeia/onomatopoeia-practice.html</t>
+          <t>yijay/synesthesia-practice.html</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/onomatopoeia/onomatopoeia-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/yijay/synesthesia-practice.html</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>62組3D雙面翻卡特訓、四選一釋義測驗、語句填空挑戰、LocalStorage錯題本</t>
+          <t>30組感官轉換試題、感官互移判定、手感記憶特訓</t>
         </is>
       </c>
     </row>
@@ -1549,237 +1540,237 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
+          <t>「賓語提前」倒裝句練習神器</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L04《愛蓮說》</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>inversion/inversion-practice.html</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/inversion/inversion-practice.html</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>3D雙面翻卡特訓、高誘答力闖關測驗、公式秘笈隨身查</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>花花語文世界專屬練習神器</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L04《愛蓮說》</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>flower/flower-practice.html</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower/flower-practice.html</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>26組3D雙面翻卡特訓、名花知己連連看配對、人比花嬌是非快打、錯題收藏本</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>詩詞常見意象練習神器(36大意象版)</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>國學常識・詩詞意象</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>flower/poetry-imagery.html</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower/poetry-imagery.html</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>36大常見意象、翻卡記憶、意象測驗、詩詞測驗、智慧錯題本</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="8" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>中外俗諺對照練習神器</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L05《生命中的碎珠》</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>proverb/proverb-practice.html</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb/proverb-practice.html</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>36組3D雙面翻卡特訓、隨機10題闖關測驗、中外俗諺對照全覽表</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>古文格言練習神器</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>國學常識・經典名言</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>proverb/proverb-aphorism.html</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb/proverb-aphorism.html</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>歷代經典古文格言、3D雙面翻卡、白話翻譯、核心道理闡釋、錯題特訓</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>狀聲詞練習神器</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>翰林國文 B3L06《鳥》</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>onomatopoeia/onomatopoeia-practice.html</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/onomatopoeia/onomatopoeia-practice.html</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>62組3D雙面翻卡特訓、四選一釋義測驗、語句填空挑戰、LocalStorage錯題本</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>專屬練習神器</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
           <t>顏色字判斷練習神器</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>翰林國文 B3L06《鳥》</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>color/color-practice.html</t>
         </is>
       </c>
-      <c r="F30" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>https://oaoadna-1313.github.io/2026_languagecorner/color/color-practice.html</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>98組3D雙面翻卡特訓、快問快答測驗、大卷練習、LocalStorage錯題本</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>跨庫整合神器</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>同義反義偏義複詞練習神器</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>複詞構造・規則判斷</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>(practicetools)</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-compound-words.html</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>偏義複詞重點突破、同義反義構詞判斷</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="9" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>跨庫整合神器</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>量詞運用練習神器</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>計量單位・語法搭配</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>(practicetools)</t>
-        </is>
-      </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-classifiers.html</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>名量詞動量詞精準搭配、生活與古漢語量詞</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="9" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>跨庫整合神器</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>連接詞運用練習神器</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>複句關係・邏輯關聯</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>(practicetools)</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-conjunctions.html</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>因果轉折遞進條件關聯詞選用、邏輯銜接強化</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="9" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>跨庫整合神器</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>詞性判斷練習神器</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>實詞虛詞・精準定位</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>(practicetools)</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-part-of-speech.html</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>十大詞性精準定位、實詞虛詞文法判定</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="9" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>跨庫整合神器</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>詞性活用判斷練習神器</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>轉品活用・文言解析</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>(practicetools)</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-pos-inflection.html</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>名詞作動詞形容詞作動詞、文言位置決定詞性</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>跨庫整合神器</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>詞性結構判斷練習神器</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>四字成語・結構拆解</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>(practicetools)</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>https://oaoadna-1313.github.io/2026_practicetools/yuwen-practice/yuwen-pos-structure.html</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>名動名動副形副形等成語結構快速分析</t>
         </is>
       </c>
     </row>

--- a/語文補給站_教材部署清單總覽.xlsx
+++ b/語文補給站_教材部署清單總覽.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\2026_語文補給站\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27EEB89C-5B6A-4D2F-9F93-E6668055BDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85DACEB-C818-490A-A375-CFBB19BA7205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -117,9 +117,6 @@
     <t>曆法大解密、10大傳統節日深度探索、20題詩詞密碼獵手、會考神射手測驗</t>
   </si>
   <si>
-    <t>詞類與詞性・AI 互動學習殿堂</t>
-  </si>
-  <si>
     <t>翰林國文 語文常識（一）</t>
   </si>
   <si>
@@ -523,6 +520,10 @@
   </si>
   <si>
     <t>字詞句層級、實詞虛詞全圖鑑（含明星動物兩袋鼠速記口訣教材圖解）、複詞音韻探索、100題流行歌詞庫(真人語音)、六大專屬練習神器內嵌</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>詞類與詞性・互動學習殿堂</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1099,19 +1100,19 @@
         <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>32</v>
-      </c>
       <c r="G6" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1122,19 +1123,19 @@
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="G7" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1145,19 +1146,19 @@
         <v>13</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G8" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1168,19 +1169,19 @@
         <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="G9" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1191,19 +1192,19 @@
         <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1214,19 +1215,19 @@
         <v>13</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="G11" s="6" t="s">
         <v>53</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1237,19 +1238,19 @@
         <v>13</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="G12" s="6" t="s">
         <v>58</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1260,19 +1261,19 @@
         <v>13</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1280,22 +1281,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1303,22 +1304,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="F15" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1326,22 +1327,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="G16" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1349,22 +1350,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="G17" s="6" t="s">
         <v>79</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1372,22 +1373,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="G18" s="6" t="s">
         <v>83</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1395,22 +1396,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="G19" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1418,22 +1419,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="G20" s="6" t="s">
         <v>91</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1441,22 +1442,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="G21" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1464,22 +1465,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D22" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="G22" s="6" t="s">
         <v>99</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1487,22 +1488,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="4" t="s">
+      <c r="F23" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="G23" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1510,22 +1511,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="G24" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1533,22 +1534,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="F25" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="G25" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1556,22 +1557,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="F26" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="G26" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1579,22 +1580,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="F27" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="6" t="s">
         <v>122</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1602,22 +1603,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="F28" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1625,22 +1626,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="E29" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="F29" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1648,22 +1649,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F30" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1671,22 +1672,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>15</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="F31" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1694,22 +1695,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="F32" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1717,22 +1718,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="4" t="s">
+      <c r="F33" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1740,22 +1741,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="F34" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="G34" s="6" t="s">
         <v>154</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1763,22 +1764,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E35" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E35" s="4" t="s">
+      <c r="F35" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="G35" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="22" customHeight="1" x14ac:dyDescent="0.3">
@@ -1786,22 +1787,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E36" s="4" t="s">
+      <c r="F36" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="G36" s="6" t="s">
         <v>162</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/語文補給站_教材部署清單總覽.xlsx
+++ b/語文補給站_教材部署清單總覽.xlsx
@@ -1066,27 +1066,27 @@
       </c>
       <c r="C15" s="10" t="inlineStr">
         <is>
-          <t>詩詞表現手法練習神器</t>
+          <t>移覺（通感）修辭練習神器</t>
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 B3L01《田園之秋選》</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
         <is>
-          <t>poetry/poetry-technique-practice.html</t>
+          <t>yijay/synesthesia-practice.html</t>
         </is>
       </c>
       <c r="F15" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry/poetry-technique-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/yijay/synesthesia-practice.html</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>41句古典詩詞名句、六大表現手法3D雙面翻卡特訓、即時測驗解析、個人錯題本</t>
+          <t>感官轉移特訓、本體與轉移感官定位、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>詩詞常見意象練習神器(51款意象版)</t>
+          <t>詩詞表現手法練習神器</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>poetry/poetry-imagery-practice.html</t>
+          <t>poetry/poetry-technique-practice.html</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry/poetry-imagery-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry/poetry-technique-practice.html</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>四大維度51款意象全收錄、3D雙面翻卡、快問快答測驗、大卷練習、錯題本</t>
+          <t>41句古典詩詞名句、六大表現手法3D雙面翻卡特訓、即時測驗解析、個人錯題本</t>
         </is>
       </c>
     </row>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>疊字詞練習神器</t>
+          <t>詩詞常見意象練習神器(51款意象版)</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
@@ -1146,17 +1146,17 @@
       </c>
       <c r="E17" s="10" t="inlineStr">
         <is>
-          <t>reduplication/reduplication-words-practice.html</t>
+          <t>poetry/poetry-imagery-practice.html</t>
         </is>
       </c>
       <c r="F17" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication/reduplication-words-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/poetry/poetry-imagery-practice.html</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>54組疊字詞深度翻卡特訓、即時測驗與詳解、大卷測驗、個人錯題本</t>
+          <t>四大維度51款意象全收錄、3D雙面翻卡、快問快答測驗、大卷練習、錯題本</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>疊字成語練習神器</t>
+          <t>疊字詞練習神器</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="E18" s="10" t="inlineStr">
         <is>
-          <t>reduplication/reduplication-idioms-practice.html</t>
+          <t>reduplication/reduplication-words-practice.html</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication/reduplication-idioms-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication/reduplication-words-practice.html</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>經典疊字成語分類探究、成語配對闖關、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>54組疊字詞深度翻卡特訓、即時測驗與詳解、大卷測驗、個人錯題本</t>
         </is>
       </c>
     </row>
@@ -1206,27 +1206,27 @@
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>節慶（詩詞句）練習神器</t>
+          <t>疊字成語練習神器</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L03《下雨天，真好》</t>
+          <t>翰林國文 B3L02《古詩選》</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
         <is>
-          <t>holiday/festival-poems.html</t>
+          <t>reduplication/reduplication-idioms-practice.html</t>
         </is>
       </c>
       <c r="F19" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/festival-poems.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/reduplication/reduplication-idioms-practice.html</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>10大傳統節日詩詞精選、文化意涵雙面翻卡、測驗挑戰、個人錯題本</t>
+          <t>經典疊字成語分類探究、成語配對闖關、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>二十四節氣練習神器</t>
+          <t>節慶（詩詞句）練習神器</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -1251,17 +1251,17 @@
       </c>
       <c r="E20" s="10" t="inlineStr">
         <is>
-          <t>holiday/24-solar-terms.html</t>
+          <t>holiday/festival-poems.html</t>
         </is>
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/24-solar-terms.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/festival-poems.html</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>太陽黃道24節氣物候天文、季節歸屬雙面翻卡、測驗挑戰、個人錯題本</t>
+          <t>10大傳統節日詩詞精選、文化意涵雙面翻卡、測驗挑戰、個人錯題本</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>季節（關鍵字詞）練習神器</t>
+          <t>二十四節氣練習神器</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
@@ -1286,17 +1286,17 @@
       </c>
       <c r="E21" s="10" t="inlineStr">
         <is>
-          <t>holiday/season-keywords.html</t>
+          <t>holiday/24-solar-terms.html</t>
         </is>
       </c>
       <c r="F21" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-keywords.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/24-solar-terms.html</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>春夏秋冬四季關鍵字詞歸納、考點特訓雙面翻卡、測驗挑戰、個人錯題本</t>
+          <t>太陽黃道24節氣物候天文、季節歸屬雙面翻卡、測驗挑戰、個人錯題本</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>季節（相關詞句）練習神器</t>
+          <t>季節（關鍵字詞）練習神器</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="E22" s="10" t="inlineStr">
         <is>
-          <t>holiday/season-verses.html</t>
+          <t>holiday/season-keywords.html</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-verses.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-keywords.html</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>古典四季景致詩詞名句深度鑑賞、雙面翻卡、測驗挑戰、個人錯題本</t>
+          <t>春夏秋冬四季關鍵字詞歸納、考點特訓雙面翻卡、測驗挑戰、個人錯題本</t>
         </is>
       </c>
     </row>
@@ -1346,27 +1346,27 @@
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>同義反義偏義複詞練習神器</t>
+          <t>季節（相關詞句）練習神器</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 語文常識（一）</t>
+          <t>翰林國文 B3L03《下雨天，真好》</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
         <is>
-          <t>pos/compound-words-practice.html</t>
+          <t>holiday/season-verses.html</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/compound-words-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/holiday/season-verses.html</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>偏義複詞重點突破、同義反義構詞判斷、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>古典四季景致詩詞名句深度鑑賞、雙面翻卡、測驗挑戰、個人錯題本</t>
         </is>
       </c>
     </row>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>量詞運用練習神器</t>
+          <t>同義反義偏義複詞練習神器</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
@@ -1391,17 +1391,17 @@
       </c>
       <c r="E24" s="10" t="inlineStr">
         <is>
-          <t>pos/classifiers-practice.html</t>
+          <t>pos/compound-words-practice.html</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/classifiers-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/compound-words-practice.html</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>名量詞動量詞精準搭配、生活與古漢語量詞、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>偏義複詞重點突破、同義反義構詞判斷、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>連接詞運用練習神器</t>
+          <t>量詞運用練習神器</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E25" s="10" t="inlineStr">
         <is>
-          <t>pos/conjunctions-practice.html</t>
+          <t>pos/classifiers-practice.html</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/conjunctions-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/classifiers-practice.html</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>因果轉折遞進條件關聯詞選用、邏輯銜接強化、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>名量詞動量詞精準搭配、生活與古漢語量詞、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>詞性判斷練習神器</t>
+          <t>連接詞運用練習神器</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="E26" s="10" t="inlineStr">
         <is>
-          <t>pos/part-of-speech-practice.html</t>
+          <t>pos/conjunctions-practice.html</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/part-of-speech-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/conjunctions-practice.html</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>十大詞性精準定位、實詞虛詞文法判定、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>因果轉折遞進條件關聯詞選用、邏輯銜接強化、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>詞性活用判斷練習神器</t>
+          <t>詞性判斷練習神器</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="E27" s="10" t="inlineStr">
         <is>
-          <t>pos/pos-inflection-practice.html</t>
+          <t>pos/part-of-speech-practice.html</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/pos-inflection-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/part-of-speech-practice.html</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>名詞作動詞形容詞作動詞、轉品活用文言位置解析、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>十大詞性精準定位、實詞虛詞文法判定、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>詞性結構判斷練習神器</t>
+          <t>詞性活用判斷練習神器</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="E28" s="10" t="inlineStr">
         <is>
-          <t>pos/pos-structure-practice.html</t>
+          <t>pos/pos-inflection-practice.html</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/pos-structure-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/pos-inflection-practice.html</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>四字成語結構拆解（名動名動、副形副形等）、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>名詞作動詞形容詞作動詞、轉品活用文言位置解析、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1556,27 +1556,27 @@
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>「賓語提前」倒裝句練習神器</t>
+          <t>詞性結構判斷練習神器</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L04《愛蓮說》</t>
+          <t>翰林國文 語文常識（一）</t>
         </is>
       </c>
       <c r="E29" s="10" t="inlineStr">
         <is>
-          <t>inversion/inversion-practice.html</t>
+          <t>pos/pos-structure-practice.html</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/inversion/inversion-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/pos/pos-structure-practice.html</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>文言語序還原特訓、之是結構辨識、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>四字成語結構拆解（名動名動、副形副形等）、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>花花語文世界專屬練習神器</t>
+          <t>「賓語提前」倒裝句練習神器</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
@@ -1601,17 +1601,17 @@
       </c>
       <c r="E30" s="10" t="inlineStr">
         <is>
-          <t>flower/flower-practice.html</t>
+          <t>inversion/inversion-practice.html</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower/flower-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/inversion/inversion-practice.html</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>植物象徵名花物語成語配對、花卉文化意涵、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>文言語序還原特訓、之是結構辨識、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>詩詞常見意象練習神器(36大意象版)</t>
+          <t>花花語文世界專屬練習神器</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -1636,17 +1636,17 @@
       </c>
       <c r="E31" s="10" t="inlineStr">
         <is>
-          <t>flower/poetry-imagery.html</t>
+          <t>flower/flower-practice.html</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower/poetry-imagery.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower/flower-practice.html</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>36大經典意象文化密碼、文人情感投射、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>植物象徵名花物語成語配對、花卉文化意涵、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1661,27 +1661,27 @@
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>中外俗諺對照練習神器</t>
+          <t>詩詞常見意象練習神器(36大意象版)</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L05《生命中的碎珠》</t>
+          <t>翰林國文 B3L04《愛蓮說》</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
         <is>
-          <t>proverb/proverb-practice.html</t>
+          <t>flower/poetry-imagery.html</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb/proverb-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/flower/poetry-imagery.html</t>
         </is>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>臺灣俗諺與世界諺語互通對照、喻體情境理解、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>36大經典意象文化密碼、文人情感投射、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>古文格言練習神器</t>
+          <t>中外俗諺對照練習神器</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -1706,17 +1706,17 @@
       </c>
       <c r="E33" s="10" t="inlineStr">
         <is>
-          <t>proverb/proverb-aphorism.html</t>
+          <t>proverb/proverb-practice.html</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb/proverb-aphorism.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb/proverb-practice.html</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>先秦兩漢唐宋經典格言名句、處世哲理深度剖析、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>臺灣俗諺與世界諺語互通對照、喻體情境理解、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1731,27 +1731,27 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>狀聲詞練習神器</t>
+          <t>古文格言練習神器</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L06《鳥》</t>
+          <t>翰林國文 B3L05《生命中的碎珠》</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
         <is>
-          <t>onomatopoeia/onomatopoeia-practice.html</t>
+          <t>proverb/proverb-aphorism.html</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/onomatopoeia/onomatopoeia-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/proverb/proverb-aphorism.html</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>八大自然與人事狀聲詞精準判讀、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>先秦兩漢唐宋經典格言名句、處世哲理深度剖析、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>顏色字判斷練習神器</t>
+          <t>詩中的鳥類練習神器</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>color/color-practice.html</t>
+          <t>bird/bird-practice.html</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/color/color-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/bird/bird-practice.html</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>98組顏色字實指非指辨析、成語借代解析、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>52種禽鳥意象情意辨識、飛羽文化密碼、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1801,7 +1801,7 @@
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>詩中的鳥類練習神器</t>
+          <t>狀聲詞練習神器</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="E36" s="10" t="inlineStr">
         <is>
-          <t>bird/bird-practice.html</t>
+          <t>onomatopoeia/onomatopoeia-practice.html</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/bird/bird-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/onomatopoeia/onomatopoeia-practice.html</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>52種禽鳥意象情意辨識、飛羽文化密碼、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>八大自然與人事狀聲詞精準判讀、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>
@@ -1836,27 +1836,27 @@
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>移覺（通感）修辭練習神器</t>
+          <t>顏色字判斷練習神器</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L01《田園之秋選》</t>
+          <t>翰林國文 B3L06《鳥》</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>yijay/synesthesia-practice.html</t>
+          <t>color/color-practice.html</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>https://oaoadna-1313.github.io/2026_languagecorner/yijay/synesthesia-practice.html</t>
+          <t>https://oaoadna-1313.github.io/2026_languagecorner/color/color-practice.html</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>感官轉移特訓、本體與轉移感官定位、雙面翻卡、測驗挑戰、錯題本</t>
+          <t>98組顏色字實指非指辨析、成語借代解析、雙面翻卡、測驗挑戰、錯題本</t>
         </is>
       </c>
     </row>

--- a/語文補給站_教材部署清單總覽.xlsx
+++ b/語文補給站_教材部署清單總覽.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="D3" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L01《田園之秋選》</t>
+          <t>翰林國文 B3L01〈田園之秋選〉</t>
         </is>
       </c>
       <c r="E3" s="10" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="D4" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 B3L02〈古詩選〉</t>
         </is>
       </c>
       <c r="E4" s="10" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 B3L02〈古詩選〉</t>
         </is>
       </c>
       <c r="E5" s="10" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 B3L02〈古詩選〉</t>
         </is>
       </c>
       <c r="E6" s="10" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="D7" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L03《下雨天，真好》</t>
+          <t>翰林國文 B3L03〈下雨天真好〉</t>
         </is>
       </c>
       <c r="E7" s="10" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="D9" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L04《愛蓮說》</t>
+          <t>翰林國文 B3L04〈愛蓮說〉</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L04《愛蓮說》</t>
+          <t>翰林國文 B3L04〈愛蓮說〉</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L05《生命中的碎珠》</t>
+          <t>翰林國文 B3L05〈生命中的碎珠〉</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L06《鳥》</t>
+          <t>翰林國文 B3L06〈鳥〉</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L06《鳥》</t>
+          <t>翰林國文 B3L06〈鳥〉</t>
         </is>
       </c>
       <c r="E13" s="10" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L06《鳥》</t>
+          <t>翰林國文 B3L06〈鳥〉</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="D15" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L01《田園之秋選》</t>
+          <t>翰林國文 B3L01〈田園之秋選〉</t>
         </is>
       </c>
       <c r="E15" s="10" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 B3L02〈古詩選〉</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 B3L02〈古詩選〉</t>
         </is>
       </c>
       <c r="E17" s="10" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 B3L02〈古詩選〉</t>
         </is>
       </c>
       <c r="E18" s="10" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L02《古詩選》</t>
+          <t>翰林國文 B3L02〈古詩選〉</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L03《下雨天，真好》</t>
+          <t>翰林國文 B3L03〈下雨天真好〉</t>
         </is>
       </c>
       <c r="E20" s="10" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L03《下雨天，真好》</t>
+          <t>翰林國文 B3L03〈下雨天真好〉</t>
         </is>
       </c>
       <c r="E21" s="10" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L03《下雨天，真好》</t>
+          <t>翰林國文 B3L03〈下雨天真好〉</t>
         </is>
       </c>
       <c r="E22" s="10" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L03《下雨天，真好》</t>
+          <t>翰林國文 B3L03〈下雨天真好〉</t>
         </is>
       </c>
       <c r="E23" s="10" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L04《愛蓮說》</t>
+          <t>翰林國文 B3L04〈愛蓮說〉</t>
         </is>
       </c>
       <c r="E30" s="10" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L04《愛蓮說》</t>
+          <t>翰林國文 B3L04〈愛蓮說〉</t>
         </is>
       </c>
       <c r="E31" s="10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L04《愛蓮說》</t>
+          <t>翰林國文 B3L04〈愛蓮說〉</t>
         </is>
       </c>
       <c r="E32" s="10" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L05《生命中的碎珠》</t>
+          <t>翰林國文 B3L05〈生命中的碎珠〉</t>
         </is>
       </c>
       <c r="E33" s="10" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L05《生命中的碎珠》</t>
+          <t>翰林國文 B3L05〈生命中的碎珠〉</t>
         </is>
       </c>
       <c r="E34" s="10" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L06《鳥》</t>
+          <t>翰林國文 B3L06〈鳥〉</t>
         </is>
       </c>
       <c r="E35" s="10" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L06《鳥》</t>
+          <t>翰林國文 B3L06〈鳥〉</t>
         </is>
       </c>
       <c r="E36" s="10" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>翰林國文 B3L06《鳥》</t>
+          <t>翰林國文 B3L06〈鳥〉</t>
         </is>
       </c>
       <c r="E37" s="10" t="inlineStr">
